--- a/DATA/MODELADO/Tensores/Exp01/metadata_tensor.xlsx
+++ b/DATA/MODELADO/Tensores/Exp01/metadata_tensor.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-28 16:08</t>
+          <t>2026-07-29 20:22</t>
         </is>
       </c>
     </row>

--- a/DATA/MODELADO/Tensores/Exp01/metadata_tensor.xlsx
+++ b/DATA/MODELADO/Tensores/Exp01/metadata_tensor.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Escalado MinMax</t>
+          <t>RobustScaler</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-29 20:22</t>
+          <t>2026-08-11 16:22</t>
         </is>
       </c>
     </row>
